--- a/diseases/d157/2020-2025.xlsx
+++ b/diseases/d157/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>36</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.6692353530639407</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>62</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.5988205263893204</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>34</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.6320556112270551</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>51</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.4925781749331506</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>23</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.4275670311241843</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>74</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.7147212734324146</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>11</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.2044885801028708</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>36</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.3477022411292828</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.1673088382659852</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>26</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.2511182852600375</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>7</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.1301290964290996</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>24</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.2318014940861885</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>8</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.1487189673475424</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>30</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.2897518676077357</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>7</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.1301290964290996</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>16</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.1545343293907923</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.05576961275532839</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>15</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.1448759338038678</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>9</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.1673088382659852</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>11</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.1062423514561697</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>10</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.185898709184428</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>13</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.1255591426300188</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>7</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.1301290964290996</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>19</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.1835095161515659</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>13</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2403805927434091</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>13</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.1248064120542257</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>6</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.1109448889584965</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>10</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.09600493234940438</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>7</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.1294357037849126</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>12</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.1152059188192853</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>9</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.1664173334377448</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>10</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.09600493234940438</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>5</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.09245407413208045</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>12</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.1152059188192853</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>7</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.1294357037849126</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>9</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.08640443911446394</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>5</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.09245407413208045</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>21</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.2016103579337492</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>8</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.1479265186113287</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>10</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.09600493234940438</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>6</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.1109448889584965</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>12</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.1152059188192853</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>8</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.1479265186113287</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>18</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.1728088782289279</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>10</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.1849081482641609</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>17</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.1632083849939875</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>7</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.1294357037849126</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>12</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.1152059188192853</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>7</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.1282802755423667</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>24</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.2288473967369031</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>5</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.09162876824454766</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>13</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.1239590065658225</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>9</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.1649317828401858</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>25</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.238382704934274</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>14</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2565605510847335</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>23</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.2193120885395321</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>11</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.2015832901380049</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>24</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.2288473967369031</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>5</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.09162876824454766</v>
       </c>
@@ -24129,9 +23952,6 @@
       <c r="O120" t="n">
         <v>19</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.1811708557500483</v>
       </c>
@@ -24525,9 +24345,6 @@
       <c r="O122" t="n">
         <v>11</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.2015832901380049</v>
       </c>
@@ -24921,9 +24738,6 @@
       <c r="O124" t="n">
         <v>25</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.238382704934274</v>
       </c>
@@ -25317,9 +25131,6 @@
       <c r="O126" t="n">
         <v>15</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.2748863047336429</v>
       </c>
@@ -25713,9 +25524,6 @@
       <c r="O128" t="n">
         <v>33</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.3146651705132418</v>
       </c>
@@ -26109,9 +25917,6 @@
       <c r="O130" t="n">
         <v>6</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.1099545218934572</v>
       </c>
@@ -26505,9 +26310,6 @@
       <c r="O132" t="n">
         <v>30</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.2860592459211289</v>
       </c>
@@ -26901,9 +26703,6 @@
       <c r="O134" t="n">
         <v>16</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.2932120583825525</v>
       </c>
@@ -27297,9 +27096,6 @@
       <c r="O136" t="n">
         <v>38</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.3623417115000966</v>
       </c>
@@ -27693,9 +27489,6 @@
       <c r="O138" t="n">
         <v>19</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.348189319329281</v>
       </c>
@@ -28089,9 +27882,6 @@
       <c r="O140" t="n">
         <v>42</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.4004829442895804</v>
       </c>
@@ -28485,9 +28275,6 @@
       <c r="O142" t="n">
         <v>38</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.6963786386585621</v>
       </c>
@@ -28881,9 +28668,6 @@
       <c r="O144" t="n">
         <v>78</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.7437540393949351</v>
       </c>
@@ -29277,9 +29061,6 @@
       <c r="O146" t="n">
         <v>46</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.8334591071442484</v>
       </c>
@@ -29673,9 +29454,6 @@
       <c r="O148" t="n">
         <v>95</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.9003464343532773</v>
       </c>
@@ -30069,9 +29847,6 @@
       <c r="O150" t="n">
         <v>52</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.9421711645978461</v>
       </c>
@@ -30465,9 +30240,6 @@
       <c r="O152" t="n">
         <v>87</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.8245277872498434</v>
       </c>
@@ -30861,9 +30633,6 @@
       <c r="O154" t="n">
         <v>67</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>1.21395130823184</v>
       </c>
@@ -31257,9 +31026,6 @@
       <c r="O156" t="n">
         <v>137</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>1.298394331646305</v>
       </c>
@@ -31653,9 +31419,6 @@
       <c r="O158" t="n">
         <v>46</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.8334591071442484</v>
       </c>
@@ -32049,9 +31812,6 @@
       <c r="O160" t="n">
         <v>152</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>1.440554294965244</v>
       </c>
@@ -32445,9 +32205,6 @@
       <c r="O162" t="n">
         <v>45</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.8153404309019822</v>
       </c>
@@ -32841,9 +32598,6 @@
       <c r="O164" t="n">
         <v>143</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>1.355258316973881</v>
       </c>
@@ -33237,9 +32991,6 @@
       <c r="O166" t="n">
         <v>44</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.7972217546597159</v>
       </c>
@@ -33633,9 +33384,6 @@
       <c r="O168" t="n">
         <v>123</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>1.165711699215296</v>
       </c>
@@ -34029,9 +33777,6 @@
       <c r="O170" t="n">
         <v>33</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.5979163159947869</v>
       </c>
@@ -34425,9 +34170,6 @@
       <c r="O172" t="n">
         <v>124</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>1.175189030103225</v>
       </c>
@@ -34821,9 +34563,6 @@
       <c r="O174" t="n">
         <v>20</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.3623735248453254</v>
       </c>
@@ -35217,9 +34956,6 @@
       <c r="O176" t="n">
         <v>75</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.7107998165946926</v>
       </c>
@@ -35613,9 +35349,6 @@
       <c r="O178" t="n">
         <v>28</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.5073229347834555</v>
       </c>
@@ -36009,9 +35742,6 @@
       <c r="O180" t="n">
         <v>60</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.5686398532757541</v>
       </c>
@@ -36405,9 +36135,6 @@
       <c r="O182" t="n">
         <v>27</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.4892042585411893</v>
       </c>
@@ -36801,9 +36528,6 @@
       <c r="O184" t="n">
         <v>49</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.4643892135085326</v>
       </c>
@@ -37197,9 +36921,6 @@
       <c r="O186" t="n">
         <v>37</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.6703910209638521</v>
       </c>
@@ -37842,7 +37563,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37989,9 +37710,6 @@
       <c r="O190" t="n">
         <v>93</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.881391772577419</v>
       </c>
@@ -38385,9 +38103,6 @@
       <c r="O192" t="n">
         <v>55</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.9965271933246448</v>
       </c>
@@ -39030,7 +38745,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39177,9 +38892,6 @@
       <c r="O196" t="n">
         <v>185</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>1.753306214266908</v>
       </c>
@@ -39573,9 +39285,6 @@
       <c r="O198" t="n">
         <v>85</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>1.524209831691371</v>
       </c>
@@ -40218,7 +39927,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40365,9 +40074,6 @@
       <c r="O202" t="n">
         <v>186</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>1.753559135812118</v>
       </c>
@@ -40761,9 +40467,6 @@
       <c r="O204" t="n">
         <v>65</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>1.165572224234578</v>
       </c>
@@ -41406,7 +41109,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41553,9 +41256,6 @@
       <c r="O208" t="n">
         <v>205</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>1.932686144309055</v>
       </c>
@@ -41949,9 +41649,6 @@
       <c r="O210" t="n">
         <v>55</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.9862534205061811</v>
       </c>
@@ -42594,7 +42291,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42741,9 +42438,6 @@
       <c r="O214" t="n">
         <v>185</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>1.744131398522805</v>
       </c>
@@ -43137,9 +42831,6 @@
       <c r="O216" t="n">
         <v>45</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.8069346167777846</v>
       </c>
@@ -43782,7 +43473,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43929,9 +43620,6 @@
       <c r="O220" t="n">
         <v>151</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>1.423588330686182</v>
       </c>
@@ -44325,9 +44013,6 @@
       <c r="O222" t="n">
         <v>29</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.52002453081235</v>
       </c>
@@ -44970,7 +44655,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45117,9 +44802,6 @@
       <c r="O226" t="n">
         <v>119</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>1.121900737428183</v>
       </c>
@@ -45513,9 +45195,6 @@
       <c r="O228" t="n">
         <v>28</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.5020926504395103</v>
       </c>
@@ -46158,7 +45837,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46305,9 +45984,6 @@
       <c r="O232" t="n">
         <v>100</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.9427737289312462</v>
       </c>
@@ -46701,9 +46377,6 @@
       <c r="O234" t="n">
         <v>27</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.4841607700666707</v>
       </c>
@@ -47346,7 +47019,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47493,9 +47166,6 @@
       <c r="O238" t="n">
         <v>101</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.9522014662205587</v>
       </c>
@@ -47889,9 +47559,6 @@
       <c r="O240" t="n">
         <v>20</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.3586376074567931</v>
       </c>
@@ -48534,7 +48201,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -48681,9 +48348,6 @@
       <c r="O244" t="n">
         <v>65</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.6128029238053101</v>
       </c>
@@ -49077,9 +48741,6 @@
       <c r="O246" t="n">
         <v>13</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.2331144448469155</v>
       </c>
@@ -49722,7 +49383,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -49869,9 +49530,6 @@
       <c r="O250" t="n">
         <v>45</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.4242481780190608</v>
       </c>
@@ -50265,9 +49923,6 @@
       <c r="O252" t="n">
         <v>16</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.2869100859654345</v>
       </c>
@@ -50910,7 +50565,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51057,9 +50712,6 @@
       <c r="O256" t="n">
         <v>67</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.631658398383935</v>
       </c>
@@ -51453,9 +51105,6 @@
       <c r="O258" t="n">
         <v>22</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.3945013682024724</v>
       </c>
@@ -52098,7 +51747,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52245,9 +51894,6 @@
       <c r="O262" t="n">
         <v>62</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.5845197119373727</v>
       </c>
@@ -52641,9 +52287,6 @@
       <c r="O264" t="n">
         <v>16</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.2869100859654345</v>
       </c>
@@ -53286,7 +52929,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53433,9 +53076,6 @@
       <c r="O268" t="n">
         <v>81</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.7636467204343094</v>
       </c>
@@ -53829,9 +53469,6 @@
       <c r="O270" t="n">
         <v>26</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.4623807880071228</v>
       </c>
@@ -54474,7 +54111,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -54621,9 +54258,6 @@
       <c r="O274" t="n">
         <v>109</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>1.02283713814673</v>
       </c>
@@ -55017,9 +54651,6 @@
       <c r="O276" t="n">
         <v>32</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.5690840467779973</v>
       </c>
@@ -55662,7 +55293,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -55809,9 +55440,6 @@
       <c r="O280" t="n">
         <v>84</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.7882414642598651</v>
       </c>
@@ -56205,9 +55833,6 @@
       <c r="O282" t="n">
         <v>32</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.5690840467779973</v>
       </c>
@@ -56850,7 +56475,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -56997,9 +56622,6 @@
       <c r="O286" t="n">
         <v>104</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.975918003369357</v>
       </c>
@@ -57393,9 +57015,6 @@
       <c r="O288" t="n">
         <v>22</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.3912452821598731</v>
       </c>
@@ -58038,7 +57657,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -58185,9 +57804,6 @@
       <c r="O292" t="n">
         <v>74</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.6944031947051194</v>
       </c>
@@ -58581,9 +58197,6 @@
       <c r="O294" t="n">
         <v>13</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.2311903940035614</v>
       </c>
@@ -59226,7 +58839,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59373,9 +58986,6 @@
       <c r="O298" t="n">
         <v>50</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.4691913477737293</v>
       </c>
@@ -59769,9 +59379,6 @@
       <c r="O300" t="n">
         <v>22</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0.3912452821598731</v>
       </c>
@@ -60414,7 +60021,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -60561,9 +60168,6 @@
       <c r="O304" t="n">
         <v>59</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0.5536457903730005</v>
       </c>
@@ -60957,9 +60561,6 @@
       <c r="O306" t="n">
         <v>19</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.3378936527744359</v>
       </c>
@@ -61602,7 +61203,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -61749,9 +61350,6 @@
       <c r="O310" t="n">
         <v>61</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0.5724134442839497</v>
       </c>
@@ -62145,9 +61743,6 @@
       <c r="O312" t="n">
         <v>17</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.302325899850811</v>
       </c>
@@ -62790,7 +62385,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -62937,9 +62532,6 @@
       <c r="O316" t="n">
         <v>42</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0.3941207321299325</v>
       </c>
@@ -63333,9 +62925,6 @@
       <c r="O318" t="n">
         <v>9</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.1600548881563117</v>
       </c>
@@ -63978,7 +63567,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -64125,9 +63714,6 @@
       <c r="O322" t="n">
         <v>37</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0.3472015973525597</v>
       </c>
@@ -64521,9 +64107,6 @@
       <c r="O324" t="n">
         <v>13</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0.2311903940035614</v>
       </c>
@@ -65166,7 +64749,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -65313,9 +64896,6 @@
       <c r="O328" t="n">
         <v>30</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0.2815148086642376</v>
       </c>
@@ -65709,9 +65289,6 @@
       <c r="O330" t="n">
         <v>21</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.3734614056980607</v>
       </c>
@@ -66354,7 +65931,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -66501,9 +66078,6 @@
       <c r="O334" t="n">
         <v>35</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.3284339434416105</v>
       </c>
@@ -66897,9 +66471,6 @@
       <c r="O336" t="n">
         <v>23</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.4090291586216856</v>
       </c>
@@ -67542,7 +67113,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -67688,9 +67259,6 @@
       </c>
       <c r="O340" t="n">
         <v>65</v>
-      </c>
-      <c r="Q340" t="n">
-        <v>0</v>
       </c>
       <c r="R340" t="n">
         <v>0.6099487521058481</v>
